--- a/reports/weather_report.xlsx
+++ b/reports/weather_report.xlsx
@@ -468,10 +468,10 @@
         <v>46269</v>
       </c>
       <c r="C3" t="n">
-        <v>24.8</v>
+        <v>24.7</v>
       </c>
       <c r="D3" t="n">
-        <v>2.1</v>
+        <v>2.7</v>
       </c>
     </row>
     <row r="4">
@@ -484,10 +484,10 @@
         <v>46270</v>
       </c>
       <c r="C4" t="n">
-        <v>21</v>
+        <v>21.2</v>
       </c>
       <c r="D4" t="n">
-        <v>0.25</v>
+        <v>0.31</v>
       </c>
     </row>
     <row r="5">
@@ -788,7 +788,7 @@
         <v>46268</v>
       </c>
       <c r="C23" t="n">
-        <v>24.7</v>
+        <v>25.3</v>
       </c>
       <c r="D23" t="n">
         <v>0</v>
@@ -804,10 +804,10 @@
         <v>46269</v>
       </c>
       <c r="C24" t="n">
-        <v>21.2</v>
+        <v>21.4</v>
       </c>
       <c r="D24" t="n">
-        <v>1.5</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="25">
@@ -820,7 +820,7 @@
         <v>46270</v>
       </c>
       <c r="C25" t="n">
-        <v>21.2</v>
+        <v>22.3</v>
       </c>
       <c r="D25" t="n">
         <v>0</v>
@@ -1236,7 +1236,7 @@
         <v>46268</v>
       </c>
       <c r="C51" t="n">
-        <v>27.2</v>
+        <v>27.7</v>
       </c>
       <c r="D51" t="n">
         <v>0</v>
@@ -1252,7 +1252,7 @@
         <v>46269</v>
       </c>
       <c r="C52" t="n">
-        <v>27.2</v>
+        <v>27.5</v>
       </c>
       <c r="D52" t="n">
         <v>0</v>

--- a/reports/weather_report.xlsx
+++ b/reports/weather_report.xlsx
@@ -449,13 +449,13 @@
         </is>
       </c>
       <c r="B2" s="1" t="n">
-        <v>46268</v>
+        <v>46273</v>
       </c>
       <c r="C2" t="n">
-        <v>23.4</v>
+        <v>28.6</v>
       </c>
       <c r="D2" t="n">
-        <v>0.3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -465,13 +465,13 @@
         </is>
       </c>
       <c r="B3" s="1" t="n">
-        <v>46269</v>
+        <v>46274</v>
       </c>
       <c r="C3" t="n">
-        <v>24.7</v>
+        <v>21.4</v>
       </c>
       <c r="D3" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
@@ -481,13 +481,13 @@
         </is>
       </c>
       <c r="B4" s="1" t="n">
-        <v>46270</v>
+        <v>46275</v>
       </c>
       <c r="C4" t="n">
-        <v>21.2</v>
+        <v>19.7</v>
       </c>
       <c r="D4" t="n">
-        <v>0.31</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -497,10 +497,10 @@
         </is>
       </c>
       <c r="B5" s="1" t="n">
-        <v>46271</v>
+        <v>46276</v>
       </c>
       <c r="C5" t="n">
-        <v>20.8</v>
+        <v>21.6</v>
       </c>
       <c r="D5" t="n">
         <v>0</v>
@@ -513,10 +513,10 @@
         </is>
       </c>
       <c r="B6" s="1" t="n">
-        <v>46272</v>
+        <v>46277</v>
       </c>
       <c r="C6" t="n">
-        <v>25.2</v>
+        <v>22.2</v>
       </c>
       <c r="D6" t="n">
         <v>0</v>
@@ -529,13 +529,13 @@
         </is>
       </c>
       <c r="B7" s="1" t="n">
-        <v>46273</v>
+        <v>46278</v>
       </c>
       <c r="C7" t="n">
-        <v>26</v>
+        <v>23.4</v>
       </c>
       <c r="D7" t="n">
-        <v>7.96</v>
+        <v>2.1</v>
       </c>
     </row>
     <row r="8">
@@ -545,10 +545,10 @@
         </is>
       </c>
       <c r="B8" s="1" t="n">
-        <v>46274</v>
+        <v>46279</v>
       </c>
       <c r="C8" t="n">
-        <v>20.7</v>
+        <v>23.1</v>
       </c>
       <c r="D8" t="n">
         <v>0</v>
@@ -561,13 +561,13 @@
         </is>
       </c>
       <c r="B9" s="1" t="n">
-        <v>46268</v>
+        <v>46273</v>
       </c>
       <c r="C9" t="n">
-        <v>20.7</v>
+        <v>21.3</v>
       </c>
       <c r="D9" t="n">
-        <v>2.4</v>
+        <v>1.9</v>
       </c>
     </row>
     <row r="10">
@@ -577,13 +577,13 @@
         </is>
       </c>
       <c r="B10" s="1" t="n">
-        <v>46269</v>
+        <v>46274</v>
       </c>
       <c r="C10" t="n">
-        <v>20.7</v>
+        <v>20.9</v>
       </c>
       <c r="D10" t="n">
-        <v>0.8</v>
+        <v>2.2</v>
       </c>
     </row>
     <row r="11">
@@ -593,13 +593,13 @@
         </is>
       </c>
       <c r="B11" s="1" t="n">
-        <v>46270</v>
+        <v>46275</v>
       </c>
       <c r="C11" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D11" t="n">
-        <v>1.1</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="12">
@@ -609,13 +609,13 @@
         </is>
       </c>
       <c r="B12" s="1" t="n">
-        <v>46271</v>
+        <v>46276</v>
       </c>
       <c r="C12" t="n">
-        <v>20</v>
+        <v>21.9</v>
       </c>
       <c r="D12" t="n">
-        <v>2.2</v>
+        <v>0.7000000000000001</v>
       </c>
     </row>
     <row r="13">
@@ -625,13 +625,13 @@
         </is>
       </c>
       <c r="B13" s="1" t="n">
-        <v>46272</v>
+        <v>46277</v>
       </c>
       <c r="C13" t="n">
-        <v>20.6</v>
+        <v>21.4</v>
       </c>
       <c r="D13" t="n">
-        <v>1.8</v>
+        <v>1.3</v>
       </c>
     </row>
     <row r="14">
@@ -641,13 +641,13 @@
         </is>
       </c>
       <c r="B14" s="1" t="n">
-        <v>46273</v>
+        <v>46278</v>
       </c>
       <c r="C14" t="n">
-        <v>21.3</v>
+        <v>20.5</v>
       </c>
       <c r="D14" t="n">
-        <v>1.2</v>
+        <v>1.1</v>
       </c>
     </row>
     <row r="15">
@@ -657,13 +657,13 @@
         </is>
       </c>
       <c r="B15" s="1" t="n">
-        <v>46274</v>
+        <v>46279</v>
       </c>
       <c r="C15" t="n">
-        <v>21.4</v>
+        <v>19.4</v>
       </c>
       <c r="D15" t="n">
-        <v>1.2</v>
+        <v>0.6000000000000001</v>
       </c>
     </row>
     <row r="16">
@@ -673,13 +673,13 @@
         </is>
       </c>
       <c r="B16" s="1" t="n">
-        <v>46268</v>
+        <v>46273</v>
       </c>
       <c r="C16" t="n">
-        <v>18</v>
+        <v>15.4</v>
       </c>
       <c r="D16" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -689,13 +689,13 @@
         </is>
       </c>
       <c r="B17" s="1" t="n">
-        <v>46269</v>
+        <v>46274</v>
       </c>
       <c r="C17" t="n">
-        <v>16.7</v>
+        <v>16.9</v>
       </c>
       <c r="D17" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="18">
@@ -705,13 +705,13 @@
         </is>
       </c>
       <c r="B18" s="1" t="n">
-        <v>46270</v>
+        <v>46275</v>
       </c>
       <c r="C18" t="n">
-        <v>12.3</v>
+        <v>16.6</v>
       </c>
       <c r="D18" t="n">
-        <v>0.8</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="19">
@@ -721,10 +721,10 @@
         </is>
       </c>
       <c r="B19" s="1" t="n">
-        <v>46271</v>
+        <v>46276</v>
       </c>
       <c r="C19" t="n">
-        <v>10.2</v>
+        <v>17.8</v>
       </c>
       <c r="D19" t="n">
         <v>0</v>
@@ -737,13 +737,13 @@
         </is>
       </c>
       <c r="B20" s="1" t="n">
-        <v>46272</v>
+        <v>46277</v>
       </c>
       <c r="C20" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="D20" t="n">
-        <v>0.3</v>
+        <v>2.7</v>
       </c>
     </row>
     <row r="21">
@@ -753,10 +753,10 @@
         </is>
       </c>
       <c r="B21" s="1" t="n">
-        <v>46273</v>
+        <v>46278</v>
       </c>
       <c r="C21" t="n">
-        <v>15.3</v>
+        <v>9.4</v>
       </c>
       <c r="D21" t="n">
         <v>0</v>
@@ -769,10 +769,10 @@
         </is>
       </c>
       <c r="B22" s="1" t="n">
-        <v>46274</v>
+        <v>46279</v>
       </c>
       <c r="C22" t="n">
-        <v>17.7</v>
+        <v>13.4</v>
       </c>
       <c r="D22" t="n">
         <v>0</v>
@@ -785,13 +785,13 @@
         </is>
       </c>
       <c r="B23" s="1" t="n">
-        <v>46268</v>
+        <v>46273</v>
       </c>
       <c r="C23" t="n">
-        <v>25.3</v>
+        <v>18.5</v>
       </c>
       <c r="D23" t="n">
-        <v>0</v>
+        <v>19.9</v>
       </c>
     </row>
     <row r="24">
@@ -801,13 +801,13 @@
         </is>
       </c>
       <c r="B24" s="1" t="n">
-        <v>46269</v>
+        <v>46274</v>
       </c>
       <c r="C24" t="n">
-        <v>21.4</v>
+        <v>19.4</v>
       </c>
       <c r="D24" t="n">
-        <v>0.3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25">
@@ -817,13 +817,13 @@
         </is>
       </c>
       <c r="B25" s="1" t="n">
-        <v>46270</v>
+        <v>46275</v>
       </c>
       <c r="C25" t="n">
-        <v>22.3</v>
+        <v>20</v>
       </c>
       <c r="D25" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="26">
@@ -833,13 +833,13 @@
         </is>
       </c>
       <c r="B26" s="1" t="n">
-        <v>46271</v>
+        <v>46276</v>
       </c>
       <c r="C26" t="n">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="D26" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
     </row>
     <row r="27">
@@ -849,10 +849,10 @@
         </is>
       </c>
       <c r="B27" s="1" t="n">
-        <v>46272</v>
+        <v>46277</v>
       </c>
       <c r="C27" t="n">
-        <v>21.3</v>
+        <v>21.8</v>
       </c>
       <c r="D27" t="n">
         <v>0</v>
@@ -865,13 +865,13 @@
         </is>
       </c>
       <c r="B28" s="1" t="n">
-        <v>46273</v>
+        <v>46278</v>
       </c>
       <c r="C28" t="n">
-        <v>18.8</v>
+        <v>23.5</v>
       </c>
       <c r="D28" t="n">
-        <v>3</v>
+        <v>3.3</v>
       </c>
     </row>
     <row r="29">
@@ -881,10 +881,10 @@
         </is>
       </c>
       <c r="B29" s="1" t="n">
-        <v>46274</v>
+        <v>46279</v>
       </c>
       <c r="C29" t="n">
-        <v>17.7</v>
+        <v>22.9</v>
       </c>
       <c r="D29" t="n">
         <v>0</v>
@@ -897,10 +897,10 @@
         </is>
       </c>
       <c r="B30" s="1" t="n">
-        <v>46268</v>
+        <v>46273</v>
       </c>
       <c r="C30" t="n">
-        <v>37.2</v>
+        <v>34.5</v>
       </c>
       <c r="D30" t="n">
         <v>0</v>
@@ -913,13 +913,13 @@
         </is>
       </c>
       <c r="B31" s="1" t="n">
-        <v>46269</v>
+        <v>46274</v>
       </c>
       <c r="C31" t="n">
-        <v>38.6</v>
+        <v>26.2</v>
       </c>
       <c r="D31" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="32">
@@ -929,10 +929,10 @@
         </is>
       </c>
       <c r="B32" s="1" t="n">
-        <v>46270</v>
+        <v>46275</v>
       </c>
       <c r="C32" t="n">
-        <v>34.4</v>
+        <v>27.3</v>
       </c>
       <c r="D32" t="n">
         <v>0</v>
@@ -945,10 +945,10 @@
         </is>
       </c>
       <c r="B33" s="1" t="n">
-        <v>46271</v>
+        <v>46276</v>
       </c>
       <c r="C33" t="n">
-        <v>35.9</v>
+        <v>29.8</v>
       </c>
       <c r="D33" t="n">
         <v>0</v>
@@ -961,10 +961,10 @@
         </is>
       </c>
       <c r="B34" s="1" t="n">
-        <v>46272</v>
+        <v>46277</v>
       </c>
       <c r="C34" t="n">
-        <v>35.5</v>
+        <v>31</v>
       </c>
       <c r="D34" t="n">
         <v>0</v>
@@ -977,10 +977,10 @@
         </is>
       </c>
       <c r="B35" s="1" t="n">
-        <v>46273</v>
+        <v>46278</v>
       </c>
       <c r="C35" t="n">
-        <v>30.5</v>
+        <v>31.6</v>
       </c>
       <c r="D35" t="n">
         <v>0</v>
@@ -993,10 +993,10 @@
         </is>
       </c>
       <c r="B36" s="1" t="n">
-        <v>46274</v>
+        <v>46279</v>
       </c>
       <c r="C36" t="n">
-        <v>27.7</v>
+        <v>33.9</v>
       </c>
       <c r="D36" t="n">
         <v>0</v>
@@ -1009,13 +1009,13 @@
         </is>
       </c>
       <c r="B37" s="1" t="n">
-        <v>46268</v>
+        <v>46273</v>
       </c>
       <c r="C37" t="n">
-        <v>24.1</v>
+        <v>22.6</v>
       </c>
       <c r="D37" t="n">
-        <v>6</v>
+        <v>4.5</v>
       </c>
     </row>
     <row r="38">
@@ -1025,13 +1025,13 @@
         </is>
       </c>
       <c r="B38" s="1" t="n">
-        <v>46269</v>
+        <v>46274</v>
       </c>
       <c r="C38" t="n">
-        <v>24.6</v>
+        <v>22.6</v>
       </c>
       <c r="D38" t="n">
-        <v>0.6</v>
+        <v>15.1</v>
       </c>
     </row>
     <row r="39">
@@ -1041,13 +1041,13 @@
         </is>
       </c>
       <c r="B39" s="1" t="n">
-        <v>46270</v>
+        <v>46275</v>
       </c>
       <c r="C39" t="n">
-        <v>25</v>
+        <v>22.9</v>
       </c>
       <c r="D39" t="n">
-        <v>4.3</v>
+        <v>8.5</v>
       </c>
     </row>
     <row r="40">
@@ -1057,13 +1057,13 @@
         </is>
       </c>
       <c r="B40" s="1" t="n">
-        <v>46271</v>
+        <v>46276</v>
       </c>
       <c r="C40" t="n">
-        <v>23.6</v>
+        <v>22</v>
       </c>
       <c r="D40" t="n">
-        <v>15.6</v>
+        <v>12.2</v>
       </c>
     </row>
     <row r="41">
@@ -1073,13 +1073,13 @@
         </is>
       </c>
       <c r="B41" s="1" t="n">
-        <v>46272</v>
+        <v>46277</v>
       </c>
       <c r="C41" t="n">
-        <v>21.8</v>
+        <v>21.2</v>
       </c>
       <c r="D41" t="n">
-        <v>14.9</v>
+        <v>6.3</v>
       </c>
     </row>
     <row r="42">
@@ -1089,13 +1089,13 @@
         </is>
       </c>
       <c r="B42" s="1" t="n">
-        <v>46273</v>
+        <v>46278</v>
       </c>
       <c r="C42" t="n">
-        <v>21.5</v>
+        <v>23.4</v>
       </c>
       <c r="D42" t="n">
-        <v>5.8</v>
+        <v>1.3</v>
       </c>
     </row>
     <row r="43">
@@ -1105,13 +1105,13 @@
         </is>
       </c>
       <c r="B43" s="1" t="n">
-        <v>46274</v>
+        <v>46279</v>
       </c>
       <c r="C43" t="n">
-        <v>22.2</v>
+        <v>21.6</v>
       </c>
       <c r="D43" t="n">
-        <v>18</v>
+        <v>11.6</v>
       </c>
     </row>
     <row r="44">
@@ -1121,13 +1121,13 @@
         </is>
       </c>
       <c r="B44" s="1" t="n">
-        <v>46268</v>
+        <v>46273</v>
       </c>
       <c r="C44" t="n">
-        <v>28.5</v>
+        <v>29.1</v>
       </c>
       <c r="D44" t="n">
-        <v>0.8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="45">
@@ -1137,13 +1137,13 @@
         </is>
       </c>
       <c r="B45" s="1" t="n">
-        <v>46269</v>
+        <v>46274</v>
       </c>
       <c r="C45" t="n">
-        <v>28.8</v>
+        <v>30.4</v>
       </c>
       <c r="D45" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
     </row>
     <row r="46">
@@ -1153,13 +1153,13 @@
         </is>
       </c>
       <c r="B46" s="1" t="n">
-        <v>46270</v>
+        <v>46275</v>
       </c>
       <c r="C46" t="n">
-        <v>27.4</v>
+        <v>25.7</v>
       </c>
       <c r="D46" t="n">
-        <v>0</v>
+        <v>2.81</v>
       </c>
     </row>
     <row r="47">
@@ -1169,10 +1169,10 @@
         </is>
       </c>
       <c r="B47" s="1" t="n">
-        <v>46271</v>
+        <v>46276</v>
       </c>
       <c r="C47" t="n">
-        <v>23.2</v>
+        <v>26.4</v>
       </c>
       <c r="D47" t="n">
         <v>0</v>
@@ -1185,10 +1185,10 @@
         </is>
       </c>
       <c r="B48" s="1" t="n">
-        <v>46272</v>
+        <v>46277</v>
       </c>
       <c r="C48" t="n">
-        <v>26.6</v>
+        <v>23.4</v>
       </c>
       <c r="D48" t="n">
         <v>0</v>
@@ -1201,13 +1201,13 @@
         </is>
       </c>
       <c r="B49" s="1" t="n">
-        <v>46273</v>
+        <v>46278</v>
       </c>
       <c r="C49" t="n">
-        <v>27.4</v>
+        <v>23.1</v>
       </c>
       <c r="D49" t="n">
-        <v>0</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="50">
@@ -1217,13 +1217,13 @@
         </is>
       </c>
       <c r="B50" s="1" t="n">
-        <v>46274</v>
+        <v>46279</v>
       </c>
       <c r="C50" t="n">
-        <v>23</v>
+        <v>27.6</v>
       </c>
       <c r="D50" t="n">
-        <v>3.9</v>
+        <v>2.4</v>
       </c>
     </row>
     <row r="51">
@@ -1233,13 +1233,13 @@
         </is>
       </c>
       <c r="B51" s="1" t="n">
-        <v>46268</v>
+        <v>46273</v>
       </c>
       <c r="C51" t="n">
-        <v>27.7</v>
+        <v>26.1</v>
       </c>
       <c r="D51" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="52">
@@ -1249,10 +1249,10 @@
         </is>
       </c>
       <c r="B52" s="1" t="n">
-        <v>46269</v>
+        <v>46274</v>
       </c>
       <c r="C52" t="n">
-        <v>27.5</v>
+        <v>21.4</v>
       </c>
       <c r="D52" t="n">
         <v>0</v>
@@ -1265,10 +1265,10 @@
         </is>
       </c>
       <c r="B53" s="1" t="n">
-        <v>46270</v>
+        <v>46275</v>
       </c>
       <c r="C53" t="n">
-        <v>24.4</v>
+        <v>22.1</v>
       </c>
       <c r="D53" t="n">
         <v>0</v>
@@ -1281,13 +1281,13 @@
         </is>
       </c>
       <c r="B54" s="1" t="n">
-        <v>46271</v>
+        <v>46276</v>
       </c>
       <c r="C54" t="n">
-        <v>30.7</v>
+        <v>22.9</v>
       </c>
       <c r="D54" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="55">
@@ -1297,13 +1297,13 @@
         </is>
       </c>
       <c r="B55" s="1" t="n">
-        <v>46272</v>
+        <v>46277</v>
       </c>
       <c r="C55" t="n">
-        <v>28.4</v>
+        <v>24.6</v>
       </c>
       <c r="D55" t="n">
-        <v>0.3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="56">
@@ -1313,13 +1313,13 @@
         </is>
       </c>
       <c r="B56" s="1" t="n">
-        <v>46273</v>
+        <v>46278</v>
       </c>
       <c r="C56" t="n">
-        <v>23.2</v>
+        <v>26.6</v>
       </c>
       <c r="D56" t="n">
-        <v>0.3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="57">
@@ -1329,10 +1329,10 @@
         </is>
       </c>
       <c r="B57" s="1" t="n">
-        <v>46274</v>
+        <v>46279</v>
       </c>
       <c r="C57" t="n">
-        <v>21.8</v>
+        <v>30</v>
       </c>
       <c r="D57" t="n">
         <v>0</v>
@@ -1345,10 +1345,10 @@
         </is>
       </c>
       <c r="B58" s="1" t="n">
-        <v>46268</v>
+        <v>46273</v>
       </c>
       <c r="C58" t="n">
-        <v>34.1</v>
+        <v>33.6</v>
       </c>
       <c r="D58" t="n">
         <v>0</v>
@@ -1361,10 +1361,10 @@
         </is>
       </c>
       <c r="B59" s="1" t="n">
-        <v>46269</v>
+        <v>46274</v>
       </c>
       <c r="C59" t="n">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="D59" t="n">
         <v>0</v>
@@ -1377,13 +1377,13 @@
         </is>
       </c>
       <c r="B60" s="1" t="n">
-        <v>46270</v>
+        <v>46275</v>
       </c>
       <c r="C60" t="n">
-        <v>33.9</v>
+        <v>31.2</v>
       </c>
       <c r="D60" t="n">
-        <v>0</v>
+        <v>10.4</v>
       </c>
     </row>
     <row r="61">
@@ -1393,13 +1393,13 @@
         </is>
       </c>
       <c r="B61" s="1" t="n">
-        <v>46271</v>
+        <v>46276</v>
       </c>
       <c r="C61" t="n">
-        <v>31.9</v>
+        <v>25.1</v>
       </c>
       <c r="D61" t="n">
-        <v>0</v>
+        <v>21.5</v>
       </c>
     </row>
     <row r="62">
@@ -1409,13 +1409,13 @@
         </is>
       </c>
       <c r="B62" s="1" t="n">
-        <v>46272</v>
+        <v>46277</v>
       </c>
       <c r="C62" t="n">
-        <v>33.2</v>
+        <v>27.6</v>
       </c>
       <c r="D62" t="n">
-        <v>0</v>
+        <v>0.6000000000000001</v>
       </c>
     </row>
     <row r="63">
@@ -1425,13 +1425,13 @@
         </is>
       </c>
       <c r="B63" s="1" t="n">
-        <v>46273</v>
+        <v>46278</v>
       </c>
       <c r="C63" t="n">
-        <v>32.4</v>
+        <v>27.8</v>
       </c>
       <c r="D63" t="n">
-        <v>0.46</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="64">
@@ -1441,13 +1441,13 @@
         </is>
       </c>
       <c r="B64" s="1" t="n">
-        <v>46274</v>
+        <v>46279</v>
       </c>
       <c r="C64" t="n">
-        <v>30.9</v>
+        <v>29.2</v>
       </c>
       <c r="D64" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="65">
@@ -1457,13 +1457,13 @@
         </is>
       </c>
       <c r="B65" s="1" t="n">
-        <v>46268</v>
+        <v>46273</v>
       </c>
       <c r="C65" t="n">
-        <v>28</v>
+        <v>27.5</v>
       </c>
       <c r="D65" t="n">
-        <v>5</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="66">
@@ -1473,13 +1473,13 @@
         </is>
       </c>
       <c r="B66" s="1" t="n">
-        <v>46269</v>
+        <v>46274</v>
       </c>
       <c r="C66" t="n">
-        <v>26.9</v>
+        <v>26.8</v>
       </c>
       <c r="D66" t="n">
-        <v>6.1</v>
+        <v>0.7000000000000001</v>
       </c>
     </row>
     <row r="67">
@@ -1489,13 +1489,13 @@
         </is>
       </c>
       <c r="B67" s="1" t="n">
-        <v>46270</v>
+        <v>46275</v>
       </c>
       <c r="C67" t="n">
-        <v>26.2</v>
+        <v>25.4</v>
       </c>
       <c r="D67" t="n">
-        <v>16.3</v>
+        <v>3.8</v>
       </c>
     </row>
     <row r="68">
@@ -1505,13 +1505,13 @@
         </is>
       </c>
       <c r="B68" s="1" t="n">
-        <v>46271</v>
+        <v>46276</v>
       </c>
       <c r="C68" t="n">
-        <v>26.1</v>
+        <v>25.8</v>
       </c>
       <c r="D68" t="n">
-        <v>18.3</v>
+        <v>4.199999999999999</v>
       </c>
     </row>
     <row r="69">
@@ -1521,13 +1521,13 @@
         </is>
       </c>
       <c r="B69" s="1" t="n">
-        <v>46272</v>
+        <v>46277</v>
       </c>
       <c r="C69" t="n">
-        <v>26</v>
+        <v>26.6</v>
       </c>
       <c r="D69" t="n">
-        <v>7.199999999999999</v>
+        <v>6.899999999999999</v>
       </c>
     </row>
     <row r="70">
@@ -1537,13 +1537,13 @@
         </is>
       </c>
       <c r="B70" s="1" t="n">
-        <v>46273</v>
+        <v>46278</v>
       </c>
       <c r="C70" t="n">
-        <v>25.6</v>
+        <v>25.9</v>
       </c>
       <c r="D70" t="n">
-        <v>4.2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="71">
@@ -1553,13 +1553,13 @@
         </is>
       </c>
       <c r="B71" s="1" t="n">
-        <v>46274</v>
+        <v>46279</v>
       </c>
       <c r="C71" t="n">
-        <v>25.5</v>
+        <v>23</v>
       </c>
       <c r="D71" t="n">
-        <v>1.2</v>
+        <v>15</v>
       </c>
     </row>
     <row r="72">
@@ -1569,13 +1569,13 @@
         </is>
       </c>
       <c r="B72" s="1" t="n">
-        <v>46268</v>
+        <v>46273</v>
       </c>
       <c r="C72" t="n">
-        <v>18.6</v>
+        <v>19.7</v>
       </c>
       <c r="D72" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="73">
@@ -1585,13 +1585,13 @@
         </is>
       </c>
       <c r="B73" s="1" t="n">
-        <v>46269</v>
+        <v>46274</v>
       </c>
       <c r="C73" t="n">
-        <v>18.6</v>
+        <v>17.1</v>
       </c>
       <c r="D73" t="n">
-        <v>0</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="74">
@@ -1601,13 +1601,13 @@
         </is>
       </c>
       <c r="B74" s="1" t="n">
-        <v>46270</v>
+        <v>46275</v>
       </c>
       <c r="C74" t="n">
-        <v>21.4</v>
+        <v>16.3</v>
       </c>
       <c r="D74" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
     </row>
     <row r="75">
@@ -1617,13 +1617,13 @@
         </is>
       </c>
       <c r="B75" s="1" t="n">
-        <v>46271</v>
+        <v>46276</v>
       </c>
       <c r="C75" t="n">
-        <v>19.7</v>
+        <v>13.9</v>
       </c>
       <c r="D75" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
     </row>
     <row r="76">
@@ -1633,10 +1633,10 @@
         </is>
       </c>
       <c r="B76" s="1" t="n">
-        <v>46272</v>
+        <v>46277</v>
       </c>
       <c r="C76" t="n">
-        <v>20.1</v>
+        <v>19.3</v>
       </c>
       <c r="D76" t="n">
         <v>0</v>
@@ -1649,10 +1649,10 @@
         </is>
       </c>
       <c r="B77" s="1" t="n">
-        <v>46273</v>
+        <v>46278</v>
       </c>
       <c r="C77" t="n">
-        <v>18.8</v>
+        <v>21.7</v>
       </c>
       <c r="D77" t="n">
         <v>0</v>
@@ -1665,10 +1665,10 @@
         </is>
       </c>
       <c r="B78" s="1" t="n">
-        <v>46274</v>
+        <v>46279</v>
       </c>
       <c r="C78" t="n">
-        <v>21.5</v>
+        <v>23.1</v>
       </c>
       <c r="D78" t="n">
         <v>0</v>
@@ -1681,13 +1681,13 @@
         </is>
       </c>
       <c r="B79" s="1" t="n">
-        <v>46269</v>
+        <v>46273</v>
       </c>
       <c r="C79" t="n">
-        <v>31.8</v>
+        <v>32.7</v>
       </c>
       <c r="D79" t="n">
-        <v>1</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="80">
@@ -1697,13 +1697,13 @@
         </is>
       </c>
       <c r="B80" s="1" t="n">
-        <v>46270</v>
+        <v>46274</v>
       </c>
       <c r="C80" t="n">
-        <v>32.9</v>
+        <v>30.5</v>
       </c>
       <c r="D80" t="n">
-        <v>0.1</v>
+        <v>8.6</v>
       </c>
     </row>
     <row r="81">
@@ -1713,13 +1713,13 @@
         </is>
       </c>
       <c r="B81" s="1" t="n">
-        <v>46271</v>
+        <v>46275</v>
       </c>
       <c r="C81" t="n">
-        <v>32.9</v>
+        <v>31.1</v>
       </c>
       <c r="D81" t="n">
-        <v>0</v>
+        <v>6.4</v>
       </c>
     </row>
     <row r="82">
@@ -1729,13 +1729,13 @@
         </is>
       </c>
       <c r="B82" s="1" t="n">
-        <v>46272</v>
+        <v>46276</v>
       </c>
       <c r="C82" t="n">
-        <v>32.3</v>
+        <v>30.7</v>
       </c>
       <c r="D82" t="n">
-        <v>0.6000000000000001</v>
+        <v>11.4</v>
       </c>
     </row>
     <row r="83">
@@ -1745,13 +1745,13 @@
         </is>
       </c>
       <c r="B83" s="1" t="n">
-        <v>46273</v>
+        <v>46277</v>
       </c>
       <c r="C83" t="n">
-        <v>31.4</v>
+        <v>31.3</v>
       </c>
       <c r="D83" t="n">
-        <v>5.399999999999999</v>
+        <v>2.4</v>
       </c>
     </row>
     <row r="84">
@@ -1761,13 +1761,13 @@
         </is>
       </c>
       <c r="B84" s="1" t="n">
-        <v>46274</v>
+        <v>46278</v>
       </c>
       <c r="C84" t="n">
-        <v>31.3</v>
+        <v>31.7</v>
       </c>
       <c r="D84" t="n">
-        <v>7.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="85">
@@ -1777,13 +1777,13 @@
         </is>
       </c>
       <c r="B85" s="1" t="n">
-        <v>46275</v>
+        <v>46279</v>
       </c>
       <c r="C85" t="n">
         <v>31.5</v>
       </c>
       <c r="D85" t="n">
-        <v>3.3</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="86">
@@ -1793,13 +1793,13 @@
         </is>
       </c>
       <c r="B86" s="1" t="n">
-        <v>46269</v>
+        <v>46274</v>
       </c>
       <c r="C86" t="n">
-        <v>22.2</v>
+        <v>18.5</v>
       </c>
       <c r="D86" t="n">
-        <v>0</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="87">
@@ -1809,10 +1809,10 @@
         </is>
       </c>
       <c r="B87" s="1" t="n">
-        <v>46270</v>
+        <v>46275</v>
       </c>
       <c r="C87" t="n">
-        <v>31.7</v>
+        <v>16.6</v>
       </c>
       <c r="D87" t="n">
         <v>0</v>
@@ -1825,13 +1825,13 @@
         </is>
       </c>
       <c r="B88" s="1" t="n">
-        <v>46271</v>
+        <v>46276</v>
       </c>
       <c r="C88" t="n">
-        <v>21.7</v>
+        <v>17.8</v>
       </c>
       <c r="D88" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="89">
@@ -1841,13 +1841,13 @@
         </is>
       </c>
       <c r="B89" s="1" t="n">
-        <v>46272</v>
+        <v>46277</v>
       </c>
       <c r="C89" t="n">
-        <v>21.2</v>
+        <v>19.9</v>
       </c>
       <c r="D89" t="n">
-        <v>0</v>
+        <v>0.6000000000000001</v>
       </c>
     </row>
     <row r="90">
@@ -1857,10 +1857,10 @@
         </is>
       </c>
       <c r="B90" s="1" t="n">
-        <v>46273</v>
+        <v>46278</v>
       </c>
       <c r="C90" t="n">
-        <v>16.8</v>
+        <v>21.8</v>
       </c>
       <c r="D90" t="n">
         <v>0</v>
@@ -1873,10 +1873,10 @@
         </is>
       </c>
       <c r="B91" s="1" t="n">
-        <v>46274</v>
+        <v>46279</v>
       </c>
       <c r="C91" t="n">
-        <v>16.6</v>
+        <v>23.1</v>
       </c>
       <c r="D91" t="n">
         <v>0</v>
@@ -1889,13 +1889,13 @@
         </is>
       </c>
       <c r="B92" s="1" t="n">
-        <v>46275</v>
+        <v>46280</v>
       </c>
       <c r="C92" t="n">
-        <v>17.5</v>
+        <v>25.6</v>
       </c>
       <c r="D92" t="n">
-        <v>0</v>
+        <v>6.600000000000001</v>
       </c>
     </row>
     <row r="93">
@@ -1905,13 +1905,13 @@
         </is>
       </c>
       <c r="B93" s="1" t="n">
-        <v>46269</v>
+        <v>46274</v>
       </c>
       <c r="C93" t="n">
-        <v>25.4</v>
+        <v>29.6</v>
       </c>
       <c r="D93" t="n">
-        <v>4.5</v>
+        <v>37.8</v>
       </c>
     </row>
     <row r="94">
@@ -1921,13 +1921,13 @@
         </is>
       </c>
       <c r="B94" s="1" t="n">
-        <v>46270</v>
+        <v>46275</v>
       </c>
       <c r="C94" t="n">
         <v>22.2</v>
       </c>
       <c r="D94" t="n">
-        <v>14.9</v>
+        <v>15</v>
       </c>
     </row>
     <row r="95">
@@ -1937,13 +1937,13 @@
         </is>
       </c>
       <c r="B95" s="1" t="n">
-        <v>46271</v>
+        <v>46276</v>
       </c>
       <c r="C95" t="n">
-        <v>23.3</v>
+        <v>24.1</v>
       </c>
       <c r="D95" t="n">
-        <v>131.13</v>
+        <v>30.81</v>
       </c>
     </row>
     <row r="96">
@@ -1953,13 +1953,13 @@
         </is>
       </c>
       <c r="B96" s="1" t="n">
-        <v>46272</v>
+        <v>46277</v>
       </c>
       <c r="C96" t="n">
-        <v>27.3</v>
+        <v>25.8</v>
       </c>
       <c r="D96" t="n">
-        <v>59.6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="97">
@@ -1969,13 +1969,13 @@
         </is>
       </c>
       <c r="B97" s="1" t="n">
-        <v>46273</v>
+        <v>46278</v>
       </c>
       <c r="C97" t="n">
-        <v>31.3</v>
+        <v>28.7</v>
       </c>
       <c r="D97" t="n">
-        <v>11.4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="98">
@@ -1985,13 +1985,13 @@
         </is>
       </c>
       <c r="B98" s="1" t="n">
-        <v>46274</v>
+        <v>46279</v>
       </c>
       <c r="C98" t="n">
-        <v>27.3</v>
+        <v>30</v>
       </c>
       <c r="D98" t="n">
-        <v>23.4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="99">
@@ -2001,13 +2001,13 @@
         </is>
       </c>
       <c r="B99" s="1" t="n">
-        <v>46275</v>
+        <v>46280</v>
       </c>
       <c r="C99" t="n">
-        <v>22.6</v>
+        <v>24.6</v>
       </c>
       <c r="D99" t="n">
-        <v>9.199999999999999</v>
+        <v>55.2</v>
       </c>
     </row>
     <row r="100">
@@ -2017,10 +2017,10 @@
         </is>
       </c>
       <c r="B100" s="1" t="n">
-        <v>46268</v>
+        <v>46273</v>
       </c>
       <c r="C100" t="n">
-        <v>25.8</v>
+        <v>25.4</v>
       </c>
       <c r="D100" t="n">
         <v>0</v>
@@ -2033,13 +2033,13 @@
         </is>
       </c>
       <c r="B101" s="1" t="n">
-        <v>46269</v>
+        <v>46274</v>
       </c>
       <c r="C101" t="n">
-        <v>21.4</v>
+        <v>22</v>
       </c>
       <c r="D101" t="n">
-        <v>0.4</v>
+        <v>20.2</v>
       </c>
     </row>
     <row r="102">
@@ -2049,10 +2049,10 @@
         </is>
       </c>
       <c r="B102" s="1" t="n">
-        <v>46270</v>
+        <v>46275</v>
       </c>
       <c r="C102" t="n">
-        <v>25.8</v>
+        <v>23.8</v>
       </c>
       <c r="D102" t="n">
         <v>0</v>
@@ -2065,10 +2065,10 @@
         </is>
       </c>
       <c r="B103" s="1" t="n">
-        <v>46271</v>
+        <v>46276</v>
       </c>
       <c r="C103" t="n">
-        <v>20</v>
+        <v>18.9</v>
       </c>
       <c r="D103" t="n">
         <v>0</v>
@@ -2081,10 +2081,10 @@
         </is>
       </c>
       <c r="B104" s="1" t="n">
-        <v>46272</v>
+        <v>46277</v>
       </c>
       <c r="C104" t="n">
-        <v>23.7</v>
+        <v>23.1</v>
       </c>
       <c r="D104" t="n">
         <v>0</v>
@@ -2097,10 +2097,10 @@
         </is>
       </c>
       <c r="B105" s="1" t="n">
-        <v>46273</v>
+        <v>46278</v>
       </c>
       <c r="C105" t="n">
-        <v>20.4</v>
+        <v>26.8</v>
       </c>
       <c r="D105" t="n">
         <v>0</v>
@@ -2113,13 +2113,13 @@
         </is>
       </c>
       <c r="B106" s="1" t="n">
-        <v>46274</v>
+        <v>46279</v>
       </c>
       <c r="C106" t="n">
-        <v>23.2</v>
+        <v>24.7</v>
       </c>
       <c r="D106" t="n">
-        <v>8.4</v>
+        <v>15.9</v>
       </c>
     </row>
   </sheetData>

--- a/reports/weather_report.xlsx
+++ b/reports/weather_report.xlsx
@@ -449,10 +449,10 @@
         </is>
       </c>
       <c r="B2" s="1" t="n">
-        <v>46273</v>
+        <v>46275</v>
       </c>
       <c r="C2" t="n">
-        <v>28.6</v>
+        <v>18.7</v>
       </c>
       <c r="D2" t="n">
         <v>0</v>
@@ -465,10 +465,10 @@
         </is>
       </c>
       <c r="B3" s="1" t="n">
-        <v>46274</v>
+        <v>46276</v>
       </c>
       <c r="C3" t="n">
-        <v>21.4</v>
+        <v>20.5</v>
       </c>
       <c r="D3" t="n">
         <v>0</v>
@@ -481,10 +481,10 @@
         </is>
       </c>
       <c r="B4" s="1" t="n">
-        <v>46275</v>
+        <v>46277</v>
       </c>
       <c r="C4" t="n">
-        <v>19.7</v>
+        <v>21.5</v>
       </c>
       <c r="D4" t="n">
         <v>0</v>
@@ -497,13 +497,13 @@
         </is>
       </c>
       <c r="B5" s="1" t="n">
-        <v>46276</v>
+        <v>46278</v>
       </c>
       <c r="C5" t="n">
-        <v>21.6</v>
+        <v>19.4</v>
       </c>
       <c r="D5" t="n">
-        <v>0</v>
+        <v>7.899999999999999</v>
       </c>
     </row>
     <row r="6">
@@ -513,10 +513,10 @@
         </is>
       </c>
       <c r="B6" s="1" t="n">
-        <v>46277</v>
+        <v>46279</v>
       </c>
       <c r="C6" t="n">
-        <v>22.2</v>
+        <v>17.8</v>
       </c>
       <c r="D6" t="n">
         <v>0</v>
@@ -529,13 +529,13 @@
         </is>
       </c>
       <c r="B7" s="1" t="n">
-        <v>46278</v>
+        <v>46280</v>
       </c>
       <c r="C7" t="n">
-        <v>23.4</v>
+        <v>21.3</v>
       </c>
       <c r="D7" t="n">
-        <v>2.1</v>
+        <v>15.3</v>
       </c>
     </row>
     <row r="8">
@@ -545,13 +545,13 @@
         </is>
       </c>
       <c r="B8" s="1" t="n">
-        <v>46279</v>
+        <v>46281</v>
       </c>
       <c r="C8" t="n">
-        <v>23.1</v>
+        <v>16.8</v>
       </c>
       <c r="D8" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
     </row>
     <row r="9">
@@ -561,13 +561,13 @@
         </is>
       </c>
       <c r="B9" s="1" t="n">
-        <v>46273</v>
+        <v>46275</v>
       </c>
       <c r="C9" t="n">
-        <v>21.3</v>
+        <v>22.2</v>
       </c>
       <c r="D9" t="n">
-        <v>1.9</v>
+        <v>1.4</v>
       </c>
     </row>
     <row r="10">
@@ -577,13 +577,13 @@
         </is>
       </c>
       <c r="B10" s="1" t="n">
-        <v>46274</v>
+        <v>46276</v>
       </c>
       <c r="C10" t="n">
-        <v>20.9</v>
+        <v>21.9</v>
       </c>
       <c r="D10" t="n">
-        <v>2.2</v>
+        <v>1.2</v>
       </c>
     </row>
     <row r="11">
@@ -593,13 +593,13 @@
         </is>
       </c>
       <c r="B11" s="1" t="n">
-        <v>46275</v>
+        <v>46277</v>
       </c>
       <c r="C11" t="n">
-        <v>21</v>
+        <v>21.4</v>
       </c>
       <c r="D11" t="n">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
     </row>
     <row r="12">
@@ -609,13 +609,13 @@
         </is>
       </c>
       <c r="B12" s="1" t="n">
-        <v>46276</v>
+        <v>46278</v>
       </c>
       <c r="C12" t="n">
-        <v>21.9</v>
+        <v>20.8</v>
       </c>
       <c r="D12" t="n">
-        <v>0.7000000000000001</v>
+        <v>1.9</v>
       </c>
     </row>
     <row r="13">
@@ -625,13 +625,13 @@
         </is>
       </c>
       <c r="B13" s="1" t="n">
-        <v>46277</v>
+        <v>46279</v>
       </c>
       <c r="C13" t="n">
-        <v>21.4</v>
+        <v>18.4</v>
       </c>
       <c r="D13" t="n">
-        <v>1.3</v>
+        <v>3.1</v>
       </c>
     </row>
     <row r="14">
@@ -641,13 +641,13 @@
         </is>
       </c>
       <c r="B14" s="1" t="n">
-        <v>46278</v>
+        <v>46280</v>
       </c>
       <c r="C14" t="n">
-        <v>20.5</v>
+        <v>20.7</v>
       </c>
       <c r="D14" t="n">
-        <v>1.1</v>
+        <v>0.6000000000000001</v>
       </c>
     </row>
     <row r="15">
@@ -657,13 +657,13 @@
         </is>
       </c>
       <c r="B15" s="1" t="n">
-        <v>46279</v>
+        <v>46281</v>
       </c>
       <c r="C15" t="n">
-        <v>19.4</v>
+        <v>20.2</v>
       </c>
       <c r="D15" t="n">
-        <v>0.6000000000000001</v>
+        <v>1.8</v>
       </c>
     </row>
     <row r="16">
@@ -673,10 +673,10 @@
         </is>
       </c>
       <c r="B16" s="1" t="n">
-        <v>46273</v>
+        <v>46275</v>
       </c>
       <c r="C16" t="n">
-        <v>15.4</v>
+        <v>18.3</v>
       </c>
       <c r="D16" t="n">
         <v>0</v>
@@ -689,13 +689,13 @@
         </is>
       </c>
       <c r="B17" s="1" t="n">
-        <v>46274</v>
+        <v>46276</v>
       </c>
       <c r="C17" t="n">
-        <v>16.9</v>
+        <v>18.1</v>
       </c>
       <c r="D17" t="n">
-        <v>2</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="18">
@@ -705,13 +705,13 @@
         </is>
       </c>
       <c r="B18" s="1" t="n">
-        <v>46275</v>
+        <v>46277</v>
       </c>
       <c r="C18" t="n">
-        <v>16.6</v>
+        <v>12.6</v>
       </c>
       <c r="D18" t="n">
-        <v>0.1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="19">
@@ -721,10 +721,10 @@
         </is>
       </c>
       <c r="B19" s="1" t="n">
-        <v>46276</v>
+        <v>46278</v>
       </c>
       <c r="C19" t="n">
-        <v>17.8</v>
+        <v>11.8</v>
       </c>
       <c r="D19" t="n">
         <v>0</v>
@@ -737,13 +737,13 @@
         </is>
       </c>
       <c r="B20" s="1" t="n">
-        <v>46277</v>
+        <v>46279</v>
       </c>
       <c r="C20" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="D20" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -753,10 +753,10 @@
         </is>
       </c>
       <c r="B21" s="1" t="n">
-        <v>46278</v>
+        <v>46280</v>
       </c>
       <c r="C21" t="n">
-        <v>9.4</v>
+        <v>18.7</v>
       </c>
       <c r="D21" t="n">
         <v>0</v>
@@ -769,10 +769,10 @@
         </is>
       </c>
       <c r="B22" s="1" t="n">
-        <v>46279</v>
+        <v>46281</v>
       </c>
       <c r="C22" t="n">
-        <v>13.4</v>
+        <v>17.9</v>
       </c>
       <c r="D22" t="n">
         <v>0</v>
@@ -785,13 +785,13 @@
         </is>
       </c>
       <c r="B23" s="1" t="n">
-        <v>46273</v>
+        <v>46275</v>
       </c>
       <c r="C23" t="n">
-        <v>18.5</v>
+        <v>20.5</v>
       </c>
       <c r="D23" t="n">
-        <v>19.9</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="24">
@@ -801,10 +801,10 @@
         </is>
       </c>
       <c r="B24" s="1" t="n">
-        <v>46274</v>
+        <v>46276</v>
       </c>
       <c r="C24" t="n">
-        <v>19.4</v>
+        <v>21.9</v>
       </c>
       <c r="D24" t="n">
         <v>0</v>
@@ -817,13 +817,13 @@
         </is>
       </c>
       <c r="B25" s="1" t="n">
-        <v>46275</v>
+        <v>46277</v>
       </c>
       <c r="C25" t="n">
-        <v>20</v>
+        <v>23.5</v>
       </c>
       <c r="D25" t="n">
-        <v>0.1</v>
+        <v>2.8</v>
       </c>
     </row>
     <row r="26">
@@ -833,13 +833,13 @@
         </is>
       </c>
       <c r="B26" s="1" t="n">
-        <v>46276</v>
+        <v>46278</v>
       </c>
       <c r="C26" t="n">
-        <v>21</v>
+        <v>21.7</v>
       </c>
       <c r="D26" t="n">
-        <v>2.6</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="27">
@@ -849,10 +849,10 @@
         </is>
       </c>
       <c r="B27" s="1" t="n">
-        <v>46277</v>
+        <v>46279</v>
       </c>
       <c r="C27" t="n">
-        <v>21.8</v>
+        <v>24.2</v>
       </c>
       <c r="D27" t="n">
         <v>0</v>
@@ -865,13 +865,13 @@
         </is>
       </c>
       <c r="B28" s="1" t="n">
-        <v>46278</v>
+        <v>46280</v>
       </c>
       <c r="C28" t="n">
-        <v>23.5</v>
+        <v>20.6</v>
       </c>
       <c r="D28" t="n">
-        <v>3.3</v>
+        <v>0.6000000000000001</v>
       </c>
     </row>
     <row r="29">
@@ -881,10 +881,10 @@
         </is>
       </c>
       <c r="B29" s="1" t="n">
-        <v>46279</v>
+        <v>46281</v>
       </c>
       <c r="C29" t="n">
-        <v>22.9</v>
+        <v>18.5</v>
       </c>
       <c r="D29" t="n">
         <v>0</v>
@@ -897,10 +897,10 @@
         </is>
       </c>
       <c r="B30" s="1" t="n">
-        <v>46273</v>
+        <v>46275</v>
       </c>
       <c r="C30" t="n">
-        <v>34.5</v>
+        <v>27.3</v>
       </c>
       <c r="D30" t="n">
         <v>0</v>
@@ -913,13 +913,13 @@
         </is>
       </c>
       <c r="B31" s="1" t="n">
-        <v>46274</v>
+        <v>46276</v>
       </c>
       <c r="C31" t="n">
-        <v>26.2</v>
+        <v>30</v>
       </c>
       <c r="D31" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="32">
@@ -929,10 +929,10 @@
         </is>
       </c>
       <c r="B32" s="1" t="n">
-        <v>46275</v>
+        <v>46277</v>
       </c>
       <c r="C32" t="n">
-        <v>27.3</v>
+        <v>31.1</v>
       </c>
       <c r="D32" t="n">
         <v>0</v>
@@ -945,10 +945,10 @@
         </is>
       </c>
       <c r="B33" s="1" t="n">
-        <v>46276</v>
+        <v>46278</v>
       </c>
       <c r="C33" t="n">
-        <v>29.8</v>
+        <v>31.6</v>
       </c>
       <c r="D33" t="n">
         <v>0</v>
@@ -961,10 +961,10 @@
         </is>
       </c>
       <c r="B34" s="1" t="n">
-        <v>46277</v>
+        <v>46279</v>
       </c>
       <c r="C34" t="n">
-        <v>31</v>
+        <v>33.2</v>
       </c>
       <c r="D34" t="n">
         <v>0</v>
@@ -977,10 +977,10 @@
         </is>
       </c>
       <c r="B35" s="1" t="n">
-        <v>46278</v>
+        <v>46280</v>
       </c>
       <c r="C35" t="n">
-        <v>31.6</v>
+        <v>35.7</v>
       </c>
       <c r="D35" t="n">
         <v>0</v>
@@ -993,7 +993,7 @@
         </is>
       </c>
       <c r="B36" s="1" t="n">
-        <v>46279</v>
+        <v>46281</v>
       </c>
       <c r="C36" t="n">
         <v>33.9</v>
@@ -1009,13 +1009,13 @@
         </is>
       </c>
       <c r="B37" s="1" t="n">
-        <v>46273</v>
+        <v>46275</v>
       </c>
       <c r="C37" t="n">
-        <v>22.6</v>
+        <v>23.2</v>
       </c>
       <c r="D37" t="n">
-        <v>4.5</v>
+        <v>13</v>
       </c>
     </row>
     <row r="38">
@@ -1025,13 +1025,13 @@
         </is>
       </c>
       <c r="B38" s="1" t="n">
-        <v>46274</v>
+        <v>46276</v>
       </c>
       <c r="C38" t="n">
-        <v>22.6</v>
+        <v>22.9</v>
       </c>
       <c r="D38" t="n">
-        <v>15.1</v>
+        <v>7.100000000000001</v>
       </c>
     </row>
     <row r="39">
@@ -1041,13 +1041,13 @@
         </is>
       </c>
       <c r="B39" s="1" t="n">
-        <v>46275</v>
+        <v>46277</v>
       </c>
       <c r="C39" t="n">
-        <v>22.9</v>
+        <v>22.6</v>
       </c>
       <c r="D39" t="n">
-        <v>8.5</v>
+        <v>7.9</v>
       </c>
     </row>
     <row r="40">
@@ -1057,13 +1057,13 @@
         </is>
       </c>
       <c r="B40" s="1" t="n">
-        <v>46276</v>
+        <v>46278</v>
       </c>
       <c r="C40" t="n">
-        <v>22</v>
+        <v>22.9</v>
       </c>
       <c r="D40" t="n">
-        <v>12.2</v>
+        <v>5.5</v>
       </c>
     </row>
     <row r="41">
@@ -1073,13 +1073,13 @@
         </is>
       </c>
       <c r="B41" s="1" t="n">
-        <v>46277</v>
+        <v>46279</v>
       </c>
       <c r="C41" t="n">
-        <v>21.2</v>
+        <v>23.1</v>
       </c>
       <c r="D41" t="n">
-        <v>6.3</v>
+        <v>8.1</v>
       </c>
     </row>
     <row r="42">
@@ -1089,13 +1089,13 @@
         </is>
       </c>
       <c r="B42" s="1" t="n">
-        <v>46278</v>
+        <v>46280</v>
       </c>
       <c r="C42" t="n">
-        <v>23.4</v>
+        <v>21.4</v>
       </c>
       <c r="D42" t="n">
-        <v>1.3</v>
+        <v>15.6</v>
       </c>
     </row>
     <row r="43">
@@ -1105,13 +1105,13 @@
         </is>
       </c>
       <c r="B43" s="1" t="n">
-        <v>46279</v>
+        <v>46281</v>
       </c>
       <c r="C43" t="n">
-        <v>21.6</v>
+        <v>21.7</v>
       </c>
       <c r="D43" t="n">
-        <v>11.6</v>
+        <v>1.8</v>
       </c>
     </row>
     <row r="44">
@@ -1121,10 +1121,10 @@
         </is>
       </c>
       <c r="B44" s="1" t="n">
-        <v>46273</v>
+        <v>46275</v>
       </c>
       <c r="C44" t="n">
-        <v>29.1</v>
+        <v>32.3</v>
       </c>
       <c r="D44" t="n">
         <v>0</v>
@@ -1137,10 +1137,10 @@
         </is>
       </c>
       <c r="B45" s="1" t="n">
-        <v>46274</v>
+        <v>46276</v>
       </c>
       <c r="C45" t="n">
-        <v>30.4</v>
+        <v>29</v>
       </c>
       <c r="D45" t="n">
         <v>0</v>
@@ -1153,13 +1153,13 @@
         </is>
       </c>
       <c r="B46" s="1" t="n">
-        <v>46275</v>
+        <v>46277</v>
       </c>
       <c r="C46" t="n">
         <v>25.7</v>
       </c>
       <c r="D46" t="n">
-        <v>2.81</v>
+        <v>1.2</v>
       </c>
     </row>
     <row r="47">
@@ -1169,13 +1169,13 @@
         </is>
       </c>
       <c r="B47" s="1" t="n">
-        <v>46276</v>
+        <v>46278</v>
       </c>
       <c r="C47" t="n">
-        <v>26.4</v>
+        <v>28</v>
       </c>
       <c r="D47" t="n">
-        <v>0</v>
+        <v>13.8</v>
       </c>
     </row>
     <row r="48">
@@ -1185,10 +1185,10 @@
         </is>
       </c>
       <c r="B48" s="1" t="n">
-        <v>46277</v>
+        <v>46279</v>
       </c>
       <c r="C48" t="n">
-        <v>23.4</v>
+        <v>28</v>
       </c>
       <c r="D48" t="n">
         <v>0</v>
@@ -1201,13 +1201,13 @@
         </is>
       </c>
       <c r="B49" s="1" t="n">
-        <v>46278</v>
+        <v>46280</v>
       </c>
       <c r="C49" t="n">
-        <v>23.1</v>
+        <v>23.7</v>
       </c>
       <c r="D49" t="n">
-        <v>0.9</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="50">
@@ -1217,13 +1217,13 @@
         </is>
       </c>
       <c r="B50" s="1" t="n">
-        <v>46279</v>
+        <v>46281</v>
       </c>
       <c r="C50" t="n">
-        <v>27.6</v>
+        <v>29.4</v>
       </c>
       <c r="D50" t="n">
-        <v>2.4</v>
+        <v>2.1</v>
       </c>
     </row>
     <row r="51">
@@ -1233,13 +1233,13 @@
         </is>
       </c>
       <c r="B51" s="1" t="n">
-        <v>46273</v>
+        <v>46275</v>
       </c>
       <c r="C51" t="n">
-        <v>26.1</v>
+        <v>21</v>
       </c>
       <c r="D51" t="n">
-        <v>0.3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="52">
@@ -1249,10 +1249,10 @@
         </is>
       </c>
       <c r="B52" s="1" t="n">
-        <v>46274</v>
+        <v>46276</v>
       </c>
       <c r="C52" t="n">
-        <v>21.4</v>
+        <v>23.2</v>
       </c>
       <c r="D52" t="n">
         <v>0</v>
@@ -1265,10 +1265,10 @@
         </is>
       </c>
       <c r="B53" s="1" t="n">
-        <v>46275</v>
+        <v>46277</v>
       </c>
       <c r="C53" t="n">
-        <v>22.1</v>
+        <v>25</v>
       </c>
       <c r="D53" t="n">
         <v>0</v>
@@ -1281,13 +1281,13 @@
         </is>
       </c>
       <c r="B54" s="1" t="n">
-        <v>46276</v>
+        <v>46278</v>
       </c>
       <c r="C54" t="n">
-        <v>22.9</v>
+        <v>22.1</v>
       </c>
       <c r="D54" t="n">
-        <v>0.2</v>
+        <v>0.6000000000000001</v>
       </c>
     </row>
     <row r="55">
@@ -1297,13 +1297,13 @@
         </is>
       </c>
       <c r="B55" s="1" t="n">
-        <v>46277</v>
+        <v>46279</v>
       </c>
       <c r="C55" t="n">
-        <v>24.6</v>
+        <v>26.3</v>
       </c>
       <c r="D55" t="n">
-        <v>0</v>
+        <v>0.6000000000000001</v>
       </c>
     </row>
     <row r="56">
@@ -1313,10 +1313,10 @@
         </is>
       </c>
       <c r="B56" s="1" t="n">
-        <v>46278</v>
+        <v>46280</v>
       </c>
       <c r="C56" t="n">
-        <v>26.6</v>
+        <v>25.6</v>
       </c>
       <c r="D56" t="n">
         <v>0</v>
@@ -1329,10 +1329,10 @@
         </is>
       </c>
       <c r="B57" s="1" t="n">
-        <v>46279</v>
+        <v>46281</v>
       </c>
       <c r="C57" t="n">
-        <v>30</v>
+        <v>20.2</v>
       </c>
       <c r="D57" t="n">
         <v>0</v>
@@ -1345,13 +1345,13 @@
         </is>
       </c>
       <c r="B58" s="1" t="n">
-        <v>46273</v>
+        <v>46275</v>
       </c>
       <c r="C58" t="n">
-        <v>33.6</v>
+        <v>27.8</v>
       </c>
       <c r="D58" t="n">
-        <v>0</v>
+        <v>27.4</v>
       </c>
     </row>
     <row r="59">
@@ -1361,13 +1361,13 @@
         </is>
       </c>
       <c r="B59" s="1" t="n">
-        <v>46274</v>
+        <v>46276</v>
       </c>
       <c r="C59" t="n">
-        <v>32</v>
+        <v>29.6</v>
       </c>
       <c r="D59" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="60">
@@ -1377,13 +1377,13 @@
         </is>
       </c>
       <c r="B60" s="1" t="n">
-        <v>46275</v>
+        <v>46277</v>
       </c>
       <c r="C60" t="n">
-        <v>31.2</v>
+        <v>29.4</v>
       </c>
       <c r="D60" t="n">
-        <v>10.4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="61">
@@ -1393,13 +1393,13 @@
         </is>
       </c>
       <c r="B61" s="1" t="n">
-        <v>46276</v>
+        <v>46278</v>
       </c>
       <c r="C61" t="n">
-        <v>25.1</v>
+        <v>29.8</v>
       </c>
       <c r="D61" t="n">
-        <v>21.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="62">
@@ -1409,13 +1409,13 @@
         </is>
       </c>
       <c r="B62" s="1" t="n">
-        <v>46277</v>
+        <v>46279</v>
       </c>
       <c r="C62" t="n">
-        <v>27.6</v>
+        <v>28.5</v>
       </c>
       <c r="D62" t="n">
-        <v>0.6000000000000001</v>
+        <v>0</v>
       </c>
     </row>
     <row r="63">
@@ -1425,13 +1425,13 @@
         </is>
       </c>
       <c r="B63" s="1" t="n">
-        <v>46278</v>
+        <v>46280</v>
       </c>
       <c r="C63" t="n">
-        <v>27.8</v>
+        <v>30.6</v>
       </c>
       <c r="D63" t="n">
-        <v>0.3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="64">
@@ -1441,13 +1441,13 @@
         </is>
       </c>
       <c r="B64" s="1" t="n">
-        <v>46279</v>
+        <v>46281</v>
       </c>
       <c r="C64" t="n">
-        <v>29.2</v>
+        <v>29.3</v>
       </c>
       <c r="D64" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
     </row>
     <row r="65">
@@ -1457,13 +1457,13 @@
         </is>
       </c>
       <c r="B65" s="1" t="n">
-        <v>46273</v>
+        <v>46275</v>
       </c>
       <c r="C65" t="n">
-        <v>27.5</v>
+        <v>24.9</v>
       </c>
       <c r="D65" t="n">
-        <v>0.9</v>
+        <v>2.7</v>
       </c>
     </row>
     <row r="66">
@@ -1473,13 +1473,13 @@
         </is>
       </c>
       <c r="B66" s="1" t="n">
-        <v>46274</v>
+        <v>46276</v>
       </c>
       <c r="C66" t="n">
-        <v>26.8</v>
+        <v>26.2</v>
       </c>
       <c r="D66" t="n">
-        <v>0.7000000000000001</v>
+        <v>1.7</v>
       </c>
     </row>
     <row r="67">
@@ -1489,13 +1489,13 @@
         </is>
       </c>
       <c r="B67" s="1" t="n">
-        <v>46275</v>
+        <v>46277</v>
       </c>
       <c r="C67" t="n">
-        <v>25.4</v>
+        <v>27.3</v>
       </c>
       <c r="D67" t="n">
-        <v>3.8</v>
+        <v>1.8</v>
       </c>
     </row>
     <row r="68">
@@ -1505,13 +1505,13 @@
         </is>
       </c>
       <c r="B68" s="1" t="n">
-        <v>46276</v>
+        <v>46278</v>
       </c>
       <c r="C68" t="n">
-        <v>25.8</v>
+        <v>27.1</v>
       </c>
       <c r="D68" t="n">
-        <v>4.199999999999999</v>
+        <v>10.4</v>
       </c>
     </row>
     <row r="69">
@@ -1521,13 +1521,13 @@
         </is>
       </c>
       <c r="B69" s="1" t="n">
-        <v>46277</v>
+        <v>46279</v>
       </c>
       <c r="C69" t="n">
-        <v>26.6</v>
+        <v>25.6</v>
       </c>
       <c r="D69" t="n">
-        <v>6.899999999999999</v>
+        <v>12.3</v>
       </c>
     </row>
     <row r="70">
@@ -1537,13 +1537,13 @@
         </is>
       </c>
       <c r="B70" s="1" t="n">
-        <v>46278</v>
+        <v>46280</v>
       </c>
       <c r="C70" t="n">
-        <v>25.9</v>
+        <v>22.9</v>
       </c>
       <c r="D70" t="n">
-        <v>6</v>
+        <v>21</v>
       </c>
     </row>
     <row r="71">
@@ -1553,13 +1553,13 @@
         </is>
       </c>
       <c r="B71" s="1" t="n">
-        <v>46279</v>
+        <v>46281</v>
       </c>
       <c r="C71" t="n">
-        <v>23</v>
+        <v>24.9</v>
       </c>
       <c r="D71" t="n">
-        <v>15</v>
+        <v>18.6</v>
       </c>
     </row>
     <row r="72">
@@ -1569,13 +1569,13 @@
         </is>
       </c>
       <c r="B72" s="1" t="n">
-        <v>46273</v>
+        <v>46275</v>
       </c>
       <c r="C72" t="n">
-        <v>19.7</v>
+        <v>18.4</v>
       </c>
       <c r="D72" t="n">
-        <v>0.2</v>
+        <v>2.2</v>
       </c>
     </row>
     <row r="73">
@@ -1585,13 +1585,13 @@
         </is>
       </c>
       <c r="B73" s="1" t="n">
-        <v>46274</v>
+        <v>46276</v>
       </c>
       <c r="C73" t="n">
-        <v>17.1</v>
+        <v>15.7</v>
       </c>
       <c r="D73" t="n">
-        <v>0.4</v>
+        <v>1.9</v>
       </c>
     </row>
     <row r="74">
@@ -1601,13 +1601,13 @@
         </is>
       </c>
       <c r="B74" s="1" t="n">
-        <v>46275</v>
+        <v>46277</v>
       </c>
       <c r="C74" t="n">
-        <v>16.3</v>
+        <v>17.9</v>
       </c>
       <c r="D74" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="75">
@@ -1617,13 +1617,13 @@
         </is>
       </c>
       <c r="B75" s="1" t="n">
-        <v>46276</v>
+        <v>46278</v>
       </c>
       <c r="C75" t="n">
-        <v>13.9</v>
+        <v>22.9</v>
       </c>
       <c r="D75" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="76">
@@ -1633,10 +1633,10 @@
         </is>
       </c>
       <c r="B76" s="1" t="n">
-        <v>46277</v>
+        <v>46279</v>
       </c>
       <c r="C76" t="n">
-        <v>19.3</v>
+        <v>24.2</v>
       </c>
       <c r="D76" t="n">
         <v>0</v>
@@ -1649,10 +1649,10 @@
         </is>
       </c>
       <c r="B77" s="1" t="n">
-        <v>46278</v>
+        <v>46280</v>
       </c>
       <c r="C77" t="n">
-        <v>21.7</v>
+        <v>26.2</v>
       </c>
       <c r="D77" t="n">
         <v>0</v>
@@ -1665,10 +1665,10 @@
         </is>
       </c>
       <c r="B78" s="1" t="n">
-        <v>46279</v>
+        <v>46281</v>
       </c>
       <c r="C78" t="n">
-        <v>23.1</v>
+        <v>25.4</v>
       </c>
       <c r="D78" t="n">
         <v>0</v>
@@ -1681,13 +1681,13 @@
         </is>
       </c>
       <c r="B79" s="1" t="n">
-        <v>46273</v>
+        <v>46275</v>
       </c>
       <c r="C79" t="n">
-        <v>32.7</v>
+        <v>32.8</v>
       </c>
       <c r="D79" t="n">
-        <v>0.1</v>
+        <v>12.8</v>
       </c>
     </row>
     <row r="80">
@@ -1697,13 +1697,13 @@
         </is>
       </c>
       <c r="B80" s="1" t="n">
-        <v>46274</v>
+        <v>46276</v>
       </c>
       <c r="C80" t="n">
-        <v>30.5</v>
+        <v>30.8</v>
       </c>
       <c r="D80" t="n">
-        <v>8.6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="81">
@@ -1713,13 +1713,13 @@
         </is>
       </c>
       <c r="B81" s="1" t="n">
-        <v>46275</v>
+        <v>46277</v>
       </c>
       <c r="C81" t="n">
-        <v>31.1</v>
+        <v>30.6</v>
       </c>
       <c r="D81" t="n">
-        <v>6.4</v>
+        <v>3.7</v>
       </c>
     </row>
     <row r="82">
@@ -1729,13 +1729,13 @@
         </is>
       </c>
       <c r="B82" s="1" t="n">
-        <v>46276</v>
+        <v>46278</v>
       </c>
       <c r="C82" t="n">
-        <v>30.7</v>
+        <v>31.6</v>
       </c>
       <c r="D82" t="n">
-        <v>11.4</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="83">
@@ -1745,13 +1745,13 @@
         </is>
       </c>
       <c r="B83" s="1" t="n">
-        <v>46277</v>
+        <v>46279</v>
       </c>
       <c r="C83" t="n">
         <v>31.3</v>
       </c>
       <c r="D83" t="n">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="84">
@@ -1761,10 +1761,10 @@
         </is>
       </c>
       <c r="B84" s="1" t="n">
-        <v>46278</v>
+        <v>46280</v>
       </c>
       <c r="C84" t="n">
-        <v>31.7</v>
+        <v>31.9</v>
       </c>
       <c r="D84" t="n">
         <v>0</v>
@@ -1777,13 +1777,13 @@
         </is>
       </c>
       <c r="B85" s="1" t="n">
-        <v>46279</v>
+        <v>46281</v>
       </c>
       <c r="C85" t="n">
-        <v>31.5</v>
+        <v>32.6</v>
       </c>
       <c r="D85" t="n">
-        <v>0.9</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="86">
@@ -1793,13 +1793,13 @@
         </is>
       </c>
       <c r="B86" s="1" t="n">
-        <v>46274</v>
+        <v>46276</v>
       </c>
       <c r="C86" t="n">
-        <v>18.5</v>
+        <v>18.2</v>
       </c>
       <c r="D86" t="n">
-        <v>0.4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="87">
@@ -1809,10 +1809,10 @@
         </is>
       </c>
       <c r="B87" s="1" t="n">
-        <v>46275</v>
+        <v>46277</v>
       </c>
       <c r="C87" t="n">
-        <v>16.6</v>
+        <v>18.9</v>
       </c>
       <c r="D87" t="n">
         <v>0</v>
@@ -1825,13 +1825,13 @@
         </is>
       </c>
       <c r="B88" s="1" t="n">
-        <v>46276</v>
+        <v>46278</v>
       </c>
       <c r="C88" t="n">
-        <v>17.8</v>
+        <v>20.8</v>
       </c>
       <c r="D88" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="89">
@@ -1841,13 +1841,13 @@
         </is>
       </c>
       <c r="B89" s="1" t="n">
-        <v>46277</v>
+        <v>46279</v>
       </c>
       <c r="C89" t="n">
-        <v>19.9</v>
+        <v>26.5</v>
       </c>
       <c r="D89" t="n">
-        <v>0.6000000000000001</v>
+        <v>0</v>
       </c>
     </row>
     <row r="90">
@@ -1857,10 +1857,10 @@
         </is>
       </c>
       <c r="B90" s="1" t="n">
-        <v>46278</v>
+        <v>46280</v>
       </c>
       <c r="C90" t="n">
-        <v>21.8</v>
+        <v>22.3</v>
       </c>
       <c r="D90" t="n">
         <v>0</v>
@@ -1873,10 +1873,10 @@
         </is>
       </c>
       <c r="B91" s="1" t="n">
-        <v>46279</v>
+        <v>46281</v>
       </c>
       <c r="C91" t="n">
-        <v>23.1</v>
+        <v>15.4</v>
       </c>
       <c r="D91" t="n">
         <v>0</v>
@@ -1889,13 +1889,13 @@
         </is>
       </c>
       <c r="B92" s="1" t="n">
-        <v>46280</v>
+        <v>46282</v>
       </c>
       <c r="C92" t="n">
-        <v>25.6</v>
+        <v>17</v>
       </c>
       <c r="D92" t="n">
-        <v>6.600000000000001</v>
+        <v>0</v>
       </c>
     </row>
     <row r="93">
@@ -1905,13 +1905,13 @@
         </is>
       </c>
       <c r="B93" s="1" t="n">
-        <v>46274</v>
+        <v>46276</v>
       </c>
       <c r="C93" t="n">
-        <v>29.6</v>
+        <v>19.6</v>
       </c>
       <c r="D93" t="n">
-        <v>37.8</v>
+        <v>85.3</v>
       </c>
     </row>
     <row r="94">
@@ -1921,13 +1921,13 @@
         </is>
       </c>
       <c r="B94" s="1" t="n">
-        <v>46275</v>
+        <v>46277</v>
       </c>
       <c r="C94" t="n">
-        <v>22.2</v>
+        <v>25.8</v>
       </c>
       <c r="D94" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
     </row>
     <row r="95">
@@ -1937,13 +1937,13 @@
         </is>
       </c>
       <c r="B95" s="1" t="n">
-        <v>46276</v>
+        <v>46278</v>
       </c>
       <c r="C95" t="n">
-        <v>24.1</v>
+        <v>26.6</v>
       </c>
       <c r="D95" t="n">
-        <v>30.81</v>
+        <v>0.33</v>
       </c>
     </row>
     <row r="96">
@@ -1953,13 +1953,13 @@
         </is>
       </c>
       <c r="B96" s="1" t="n">
-        <v>46277</v>
+        <v>46279</v>
       </c>
       <c r="C96" t="n">
-        <v>25.8</v>
+        <v>30.1</v>
       </c>
       <c r="D96" t="n">
-        <v>1</v>
+        <v>0.6000000000000001</v>
       </c>
     </row>
     <row r="97">
@@ -1969,13 +1969,13 @@
         </is>
       </c>
       <c r="B97" s="1" t="n">
-        <v>46278</v>
+        <v>46280</v>
       </c>
       <c r="C97" t="n">
-        <v>28.7</v>
+        <v>27.9</v>
       </c>
       <c r="D97" t="n">
-        <v>0</v>
+        <v>22.5</v>
       </c>
     </row>
     <row r="98">
@@ -1985,13 +1985,13 @@
         </is>
       </c>
       <c r="B98" s="1" t="n">
-        <v>46279</v>
+        <v>46281</v>
       </c>
       <c r="C98" t="n">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="D98" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="99">
@@ -2001,13 +2001,13 @@
         </is>
       </c>
       <c r="B99" s="1" t="n">
-        <v>46280</v>
+        <v>46282</v>
       </c>
       <c r="C99" t="n">
-        <v>24.6</v>
+        <v>25.1</v>
       </c>
       <c r="D99" t="n">
-        <v>55.2</v>
+        <v>2</v>
       </c>
     </row>
     <row r="100">
@@ -2017,10 +2017,10 @@
         </is>
       </c>
       <c r="B100" s="1" t="n">
-        <v>46273</v>
+        <v>46275</v>
       </c>
       <c r="C100" t="n">
-        <v>25.4</v>
+        <v>27.1</v>
       </c>
       <c r="D100" t="n">
         <v>0</v>
@@ -2033,13 +2033,13 @@
         </is>
       </c>
       <c r="B101" s="1" t="n">
-        <v>46274</v>
+        <v>46276</v>
       </c>
       <c r="C101" t="n">
-        <v>22</v>
+        <v>20.9</v>
       </c>
       <c r="D101" t="n">
-        <v>20.2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="102">
@@ -2049,10 +2049,10 @@
         </is>
       </c>
       <c r="B102" s="1" t="n">
-        <v>46275</v>
+        <v>46277</v>
       </c>
       <c r="C102" t="n">
-        <v>23.8</v>
+        <v>24.7</v>
       </c>
       <c r="D102" t="n">
         <v>0</v>
@@ -2065,13 +2065,13 @@
         </is>
       </c>
       <c r="B103" s="1" t="n">
-        <v>46276</v>
+        <v>46278</v>
       </c>
       <c r="C103" t="n">
-        <v>18.9</v>
+        <v>28.1</v>
       </c>
       <c r="D103" t="n">
-        <v>0</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="104">
@@ -2081,10 +2081,10 @@
         </is>
       </c>
       <c r="B104" s="1" t="n">
-        <v>46277</v>
+        <v>46279</v>
       </c>
       <c r="C104" t="n">
-        <v>23.1</v>
+        <v>19.7</v>
       </c>
       <c r="D104" t="n">
         <v>0</v>
@@ -2097,13 +2097,13 @@
         </is>
       </c>
       <c r="B105" s="1" t="n">
-        <v>46278</v>
+        <v>46280</v>
       </c>
       <c r="C105" t="n">
-        <v>26.8</v>
+        <v>29.9</v>
       </c>
       <c r="D105" t="n">
-        <v>0</v>
+        <v>8.5</v>
       </c>
     </row>
     <row r="106">
@@ -2113,13 +2113,13 @@
         </is>
       </c>
       <c r="B106" s="1" t="n">
-        <v>46279</v>
+        <v>46281</v>
       </c>
       <c r="C106" t="n">
-        <v>24.7</v>
+        <v>23</v>
       </c>
       <c r="D106" t="n">
-        <v>15.9</v>
+        <v>3.9</v>
       </c>
     </row>
   </sheetData>

--- a/reports/weather_report.xlsx
+++ b/reports/weather_report.xlsx
@@ -468,7 +468,7 @@
         <v>46276</v>
       </c>
       <c r="C3" t="n">
-        <v>20.5</v>
+        <v>20.9</v>
       </c>
       <c r="D3" t="n">
         <v>0</v>
@@ -484,10 +484,10 @@
         <v>46277</v>
       </c>
       <c r="C4" t="n">
-        <v>21.5</v>
+        <v>21.6</v>
       </c>
       <c r="D4" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="5">
@@ -500,10 +500,10 @@
         <v>46278</v>
       </c>
       <c r="C5" t="n">
-        <v>19.4</v>
+        <v>19.8</v>
       </c>
       <c r="D5" t="n">
-        <v>7.899999999999999</v>
+        <v>2.7</v>
       </c>
     </row>
     <row r="6">
@@ -516,10 +516,10 @@
         <v>46279</v>
       </c>
       <c r="C6" t="n">
-        <v>17.8</v>
+        <v>18.2</v>
       </c>
       <c r="D6" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
     </row>
     <row r="7">
@@ -532,10 +532,10 @@
         <v>46280</v>
       </c>
       <c r="C7" t="n">
-        <v>21.3</v>
+        <v>22.2</v>
       </c>
       <c r="D7" t="n">
-        <v>15.3</v>
+        <v>0.8999999999999999</v>
       </c>
     </row>
     <row r="8">
@@ -548,10 +548,10 @@
         <v>46281</v>
       </c>
       <c r="C8" t="n">
-        <v>16.8</v>
+        <v>18.1</v>
       </c>
       <c r="D8" t="n">
-        <v>2.7</v>
+        <v>12.3</v>
       </c>
     </row>
     <row r="9">
@@ -564,10 +564,10 @@
         <v>46275</v>
       </c>
       <c r="C9" t="n">
-        <v>22.2</v>
+        <v>21.8</v>
       </c>
       <c r="D9" t="n">
-        <v>1.4</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="10">
@@ -580,10 +580,10 @@
         <v>46276</v>
       </c>
       <c r="C10" t="n">
-        <v>21.9</v>
+        <v>22</v>
       </c>
       <c r="D10" t="n">
-        <v>1.2</v>
+        <v>1.1</v>
       </c>
     </row>
     <row r="11">
@@ -596,10 +596,10 @@
         <v>46277</v>
       </c>
       <c r="C11" t="n">
-        <v>21.4</v>
+        <v>21.6</v>
       </c>
       <c r="D11" t="n">
-        <v>1.6</v>
+        <v>1.3</v>
       </c>
     </row>
     <row r="12">
@@ -612,10 +612,10 @@
         <v>46278</v>
       </c>
       <c r="C12" t="n">
-        <v>20.8</v>
+        <v>20.3</v>
       </c>
       <c r="D12" t="n">
-        <v>1.9</v>
+        <v>1.3</v>
       </c>
     </row>
     <row r="13">
@@ -628,10 +628,10 @@
         <v>46279</v>
       </c>
       <c r="C13" t="n">
-        <v>18.4</v>
+        <v>18.6</v>
       </c>
       <c r="D13" t="n">
-        <v>3.1</v>
+        <v>1.8</v>
       </c>
     </row>
     <row r="14">
@@ -644,7 +644,7 @@
         <v>46280</v>
       </c>
       <c r="C14" t="n">
-        <v>20.7</v>
+        <v>20.8</v>
       </c>
       <c r="D14" t="n">
         <v>0.6000000000000001</v>
@@ -660,10 +660,10 @@
         <v>46281</v>
       </c>
       <c r="C15" t="n">
-        <v>20.2</v>
+        <v>20.1</v>
       </c>
       <c r="D15" t="n">
-        <v>1.8</v>
+        <v>2.7</v>
       </c>
     </row>
     <row r="16">
@@ -676,7 +676,7 @@
         <v>46275</v>
       </c>
       <c r="C16" t="n">
-        <v>18.3</v>
+        <v>18.5</v>
       </c>
       <c r="D16" t="n">
         <v>0</v>
@@ -692,10 +692,10 @@
         <v>46276</v>
       </c>
       <c r="C17" t="n">
-        <v>18.1</v>
+        <v>16.9</v>
       </c>
       <c r="D17" t="n">
-        <v>0.3</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="18">
@@ -708,10 +708,10 @@
         <v>46277</v>
       </c>
       <c r="C18" t="n">
-        <v>12.6</v>
+        <v>13.1</v>
       </c>
       <c r="D18" t="n">
-        <v>2</v>
+        <v>0.7000000000000001</v>
       </c>
     </row>
     <row r="19">
@@ -724,7 +724,7 @@
         <v>46278</v>
       </c>
       <c r="C19" t="n">
-        <v>11.8</v>
+        <v>11.9</v>
       </c>
       <c r="D19" t="n">
         <v>0</v>
@@ -740,7 +740,7 @@
         <v>46279</v>
       </c>
       <c r="C20" t="n">
-        <v>13.2</v>
+        <v>13</v>
       </c>
       <c r="D20" t="n">
         <v>0</v>
@@ -756,7 +756,7 @@
         <v>46280</v>
       </c>
       <c r="C21" t="n">
-        <v>18.7</v>
+        <v>15.9</v>
       </c>
       <c r="D21" t="n">
         <v>0</v>
@@ -772,7 +772,7 @@
         <v>46281</v>
       </c>
       <c r="C22" t="n">
-        <v>17.9</v>
+        <v>13.3</v>
       </c>
       <c r="D22" t="n">
         <v>0</v>
@@ -788,10 +788,10 @@
         <v>46275</v>
       </c>
       <c r="C23" t="n">
-        <v>20.5</v>
+        <v>20.3</v>
       </c>
       <c r="D23" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="24">
@@ -804,10 +804,10 @@
         <v>46276</v>
       </c>
       <c r="C24" t="n">
-        <v>21.9</v>
+        <v>21.8</v>
       </c>
       <c r="D24" t="n">
-        <v>0</v>
+        <v>0.7</v>
       </c>
     </row>
     <row r="25">
@@ -820,7 +820,7 @@
         <v>46277</v>
       </c>
       <c r="C25" t="n">
-        <v>23.5</v>
+        <v>23.6</v>
       </c>
       <c r="D25" t="n">
         <v>2.8</v>
@@ -900,7 +900,7 @@
         <v>46275</v>
       </c>
       <c r="C30" t="n">
-        <v>27.3</v>
+        <v>27.4</v>
       </c>
       <c r="D30" t="n">
         <v>0</v>
@@ -916,7 +916,7 @@
         <v>46276</v>
       </c>
       <c r="C31" t="n">
-        <v>30</v>
+        <v>30.3</v>
       </c>
       <c r="D31" t="n">
         <v>0</v>
@@ -932,7 +932,7 @@
         <v>46277</v>
       </c>
       <c r="C32" t="n">
-        <v>31.1</v>
+        <v>30.9</v>
       </c>
       <c r="D32" t="n">
         <v>0</v>
@@ -948,7 +948,7 @@
         <v>46278</v>
       </c>
       <c r="C33" t="n">
-        <v>31.6</v>
+        <v>31.8</v>
       </c>
       <c r="D33" t="n">
         <v>0</v>
@@ -964,7 +964,7 @@
         <v>46279</v>
       </c>
       <c r="C34" t="n">
-        <v>33.2</v>
+        <v>33.8</v>
       </c>
       <c r="D34" t="n">
         <v>0</v>
@@ -980,7 +980,7 @@
         <v>46280</v>
       </c>
       <c r="C35" t="n">
-        <v>35.7</v>
+        <v>35.5</v>
       </c>
       <c r="D35" t="n">
         <v>0</v>
@@ -996,7 +996,7 @@
         <v>46281</v>
       </c>
       <c r="C36" t="n">
-        <v>33.9</v>
+        <v>32.8</v>
       </c>
       <c r="D36" t="n">
         <v>0</v>
@@ -1012,10 +1012,10 @@
         <v>46275</v>
       </c>
       <c r="C37" t="n">
-        <v>23.2</v>
+        <v>23.8</v>
       </c>
       <c r="D37" t="n">
-        <v>13</v>
+        <v>10.3</v>
       </c>
     </row>
     <row r="38">
@@ -1028,10 +1028,10 @@
         <v>46276</v>
       </c>
       <c r="C38" t="n">
-        <v>22.9</v>
+        <v>23.6</v>
       </c>
       <c r="D38" t="n">
-        <v>7.100000000000001</v>
+        <v>16.4</v>
       </c>
     </row>
     <row r="39">
@@ -1044,10 +1044,10 @@
         <v>46277</v>
       </c>
       <c r="C39" t="n">
-        <v>22.6</v>
+        <v>23</v>
       </c>
       <c r="D39" t="n">
-        <v>7.9</v>
+        <v>4.9</v>
       </c>
     </row>
     <row r="40">
@@ -1060,10 +1060,10 @@
         <v>46278</v>
       </c>
       <c r="C40" t="n">
-        <v>22.9</v>
+        <v>22.7</v>
       </c>
       <c r="D40" t="n">
-        <v>5.5</v>
+        <v>3.5</v>
       </c>
     </row>
     <row r="41">
@@ -1076,10 +1076,10 @@
         <v>46279</v>
       </c>
       <c r="C41" t="n">
-        <v>23.1</v>
+        <v>22.7</v>
       </c>
       <c r="D41" t="n">
-        <v>8.1</v>
+        <v>9.699999999999999</v>
       </c>
     </row>
     <row r="42">
@@ -1092,10 +1092,10 @@
         <v>46280</v>
       </c>
       <c r="C42" t="n">
-        <v>21.4</v>
+        <v>21.8</v>
       </c>
       <c r="D42" t="n">
-        <v>15.6</v>
+        <v>13.2</v>
       </c>
     </row>
     <row r="43">
@@ -1111,7 +1111,7 @@
         <v>21.7</v>
       </c>
       <c r="D43" t="n">
-        <v>1.8</v>
+        <v>1.9</v>
       </c>
     </row>
     <row r="44">
@@ -1124,7 +1124,7 @@
         <v>46275</v>
       </c>
       <c r="C44" t="n">
-        <v>32.3</v>
+        <v>31.8</v>
       </c>
       <c r="D44" t="n">
         <v>0</v>
@@ -1156,10 +1156,10 @@
         <v>46277</v>
       </c>
       <c r="C46" t="n">
-        <v>25.7</v>
+        <v>25.5</v>
       </c>
       <c r="D46" t="n">
-        <v>1.2</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="47">
@@ -1172,10 +1172,10 @@
         <v>46278</v>
       </c>
       <c r="C47" t="n">
-        <v>28</v>
+        <v>28.9</v>
       </c>
       <c r="D47" t="n">
-        <v>13.8</v>
+        <v>18.3</v>
       </c>
     </row>
     <row r="48">
@@ -1188,7 +1188,7 @@
         <v>46279</v>
       </c>
       <c r="C48" t="n">
-        <v>28</v>
+        <v>26.7</v>
       </c>
       <c r="D48" t="n">
         <v>0</v>
@@ -1204,10 +1204,10 @@
         <v>46280</v>
       </c>
       <c r="C49" t="n">
-        <v>23.7</v>
+        <v>22.7</v>
       </c>
       <c r="D49" t="n">
-        <v>0.3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="50">
@@ -1220,10 +1220,10 @@
         <v>46281</v>
       </c>
       <c r="C50" t="n">
-        <v>29.4</v>
+        <v>27.8</v>
       </c>
       <c r="D50" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="51">
@@ -1236,7 +1236,7 @@
         <v>46275</v>
       </c>
       <c r="C51" t="n">
-        <v>21</v>
+        <v>21.4</v>
       </c>
       <c r="D51" t="n">
         <v>0</v>
@@ -1252,7 +1252,7 @@
         <v>46276</v>
       </c>
       <c r="C52" t="n">
-        <v>23.2</v>
+        <v>23.9</v>
       </c>
       <c r="D52" t="n">
         <v>0</v>
@@ -1268,7 +1268,7 @@
         <v>46277</v>
       </c>
       <c r="C53" t="n">
-        <v>25</v>
+        <v>24.8</v>
       </c>
       <c r="D53" t="n">
         <v>0</v>
@@ -1284,10 +1284,10 @@
         <v>46278</v>
       </c>
       <c r="C54" t="n">
-        <v>22.1</v>
+        <v>24.4</v>
       </c>
       <c r="D54" t="n">
-        <v>0.6000000000000001</v>
+        <v>0</v>
       </c>
     </row>
     <row r="55">
@@ -1300,10 +1300,10 @@
         <v>46279</v>
       </c>
       <c r="C55" t="n">
-        <v>26.3</v>
+        <v>26.7</v>
       </c>
       <c r="D55" t="n">
-        <v>0.6000000000000001</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="56">
@@ -1316,7 +1316,7 @@
         <v>46280</v>
       </c>
       <c r="C56" t="n">
-        <v>25.6</v>
+        <v>29.9</v>
       </c>
       <c r="D56" t="n">
         <v>0</v>
@@ -1332,7 +1332,7 @@
         <v>46281</v>
       </c>
       <c r="C57" t="n">
-        <v>20.2</v>
+        <v>22.2</v>
       </c>
       <c r="D57" t="n">
         <v>0</v>
@@ -1348,10 +1348,10 @@
         <v>46275</v>
       </c>
       <c r="C58" t="n">
-        <v>27.8</v>
+        <v>27.7</v>
       </c>
       <c r="D58" t="n">
-        <v>27.4</v>
+        <v>36</v>
       </c>
     </row>
     <row r="59">
@@ -1364,10 +1364,10 @@
         <v>46276</v>
       </c>
       <c r="C59" t="n">
-        <v>29.6</v>
+        <v>29.1</v>
       </c>
       <c r="D59" t="n">
-        <v>0.3</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="60">
@@ -1380,7 +1380,7 @@
         <v>46277</v>
       </c>
       <c r="C60" t="n">
-        <v>29.4</v>
+        <v>29.7</v>
       </c>
       <c r="D60" t="n">
         <v>0</v>
@@ -1396,7 +1396,7 @@
         <v>46278</v>
       </c>
       <c r="C61" t="n">
-        <v>29.8</v>
+        <v>29.6</v>
       </c>
       <c r="D61" t="n">
         <v>0</v>
@@ -1412,7 +1412,7 @@
         <v>46279</v>
       </c>
       <c r="C62" t="n">
-        <v>28.5</v>
+        <v>30</v>
       </c>
       <c r="D62" t="n">
         <v>0</v>
@@ -1428,7 +1428,7 @@
         <v>46280</v>
       </c>
       <c r="C63" t="n">
-        <v>30.6</v>
+        <v>30.9</v>
       </c>
       <c r="D63" t="n">
         <v>0</v>
@@ -1444,10 +1444,10 @@
         <v>46281</v>
       </c>
       <c r="C64" t="n">
-        <v>29.3</v>
+        <v>30.6</v>
       </c>
       <c r="D64" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="65">
@@ -1460,10 +1460,10 @@
         <v>46275</v>
       </c>
       <c r="C65" t="n">
-        <v>24.9</v>
+        <v>25</v>
       </c>
       <c r="D65" t="n">
-        <v>2.7</v>
+        <v>9.700000000000001</v>
       </c>
     </row>
     <row r="66">
@@ -1476,10 +1476,10 @@
         <v>46276</v>
       </c>
       <c r="C66" t="n">
-        <v>26.2</v>
+        <v>26.3</v>
       </c>
       <c r="D66" t="n">
-        <v>1.7</v>
+        <v>1.6</v>
       </c>
     </row>
     <row r="67">
@@ -1492,10 +1492,10 @@
         <v>46277</v>
       </c>
       <c r="C67" t="n">
-        <v>27.3</v>
+        <v>26.8</v>
       </c>
       <c r="D67" t="n">
-        <v>1.8</v>
+        <v>15.1</v>
       </c>
     </row>
     <row r="68">
@@ -1508,10 +1508,10 @@
         <v>46278</v>
       </c>
       <c r="C68" t="n">
-        <v>27.1</v>
+        <v>25.2</v>
       </c>
       <c r="D68" t="n">
-        <v>10.4</v>
+        <v>8.199999999999999</v>
       </c>
     </row>
     <row r="69">
@@ -1524,10 +1524,10 @@
         <v>46279</v>
       </c>
       <c r="C69" t="n">
-        <v>25.6</v>
+        <v>24.3</v>
       </c>
       <c r="D69" t="n">
-        <v>12.3</v>
+        <v>16.2</v>
       </c>
     </row>
     <row r="70">
@@ -1540,10 +1540,10 @@
         <v>46280</v>
       </c>
       <c r="C70" t="n">
-        <v>22.9</v>
+        <v>25.2</v>
       </c>
       <c r="D70" t="n">
-        <v>21</v>
+        <v>20.9</v>
       </c>
     </row>
     <row r="71">
@@ -1556,10 +1556,10 @@
         <v>46281</v>
       </c>
       <c r="C71" t="n">
-        <v>24.9</v>
+        <v>24.5</v>
       </c>
       <c r="D71" t="n">
-        <v>18.6</v>
+        <v>10.9</v>
       </c>
     </row>
     <row r="72">
@@ -1572,10 +1572,10 @@
         <v>46275</v>
       </c>
       <c r="C72" t="n">
-        <v>18.4</v>
+        <v>17.6</v>
       </c>
       <c r="D72" t="n">
-        <v>2.2</v>
+        <v>1.7</v>
       </c>
     </row>
     <row r="73">
@@ -1591,7 +1591,7 @@
         <v>15.7</v>
       </c>
       <c r="D73" t="n">
-        <v>1.9</v>
+        <v>1.6</v>
       </c>
     </row>
     <row r="74">
@@ -1604,10 +1604,10 @@
         <v>46277</v>
       </c>
       <c r="C74" t="n">
-        <v>17.9</v>
+        <v>17.3</v>
       </c>
       <c r="D74" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="75">
@@ -1620,7 +1620,7 @@
         <v>46278</v>
       </c>
       <c r="C75" t="n">
-        <v>22.9</v>
+        <v>22.8</v>
       </c>
       <c r="D75" t="n">
         <v>0</v>
@@ -1636,7 +1636,7 @@
         <v>46279</v>
       </c>
       <c r="C76" t="n">
-        <v>24.2</v>
+        <v>24.4</v>
       </c>
       <c r="D76" t="n">
         <v>0</v>
@@ -1652,7 +1652,7 @@
         <v>46280</v>
       </c>
       <c r="C77" t="n">
-        <v>26.2</v>
+        <v>26.5</v>
       </c>
       <c r="D77" t="n">
         <v>0</v>
@@ -1668,7 +1668,7 @@
         <v>46281</v>
       </c>
       <c r="C78" t="n">
-        <v>25.4</v>
+        <v>23.9</v>
       </c>
       <c r="D78" t="n">
         <v>0</v>
@@ -1681,13 +1681,13 @@
         </is>
       </c>
       <c r="B79" s="1" t="n">
-        <v>46275</v>
+        <v>46276</v>
       </c>
       <c r="C79" t="n">
-        <v>32.8</v>
+        <v>28.6</v>
       </c>
       <c r="D79" t="n">
-        <v>12.8</v>
+        <v>16.3</v>
       </c>
     </row>
     <row r="80">
@@ -1697,13 +1697,13 @@
         </is>
       </c>
       <c r="B80" s="1" t="n">
-        <v>46276</v>
+        <v>46277</v>
       </c>
       <c r="C80" t="n">
-        <v>30.8</v>
+        <v>30.4</v>
       </c>
       <c r="D80" t="n">
-        <v>5</v>
+        <v>2.8</v>
       </c>
     </row>
     <row r="81">
@@ -1713,13 +1713,13 @@
         </is>
       </c>
       <c r="B81" s="1" t="n">
-        <v>46277</v>
+        <v>46278</v>
       </c>
       <c r="C81" t="n">
-        <v>30.6</v>
+        <v>31.3</v>
       </c>
       <c r="D81" t="n">
-        <v>3.7</v>
+        <v>1</v>
       </c>
     </row>
     <row r="82">
@@ -1729,13 +1729,13 @@
         </is>
       </c>
       <c r="B82" s="1" t="n">
-        <v>46278</v>
+        <v>46279</v>
       </c>
       <c r="C82" t="n">
-        <v>31.6</v>
+        <v>30.8</v>
       </c>
       <c r="D82" t="n">
-        <v>0.9</v>
+        <v>2</v>
       </c>
     </row>
     <row r="83">
@@ -1745,13 +1745,13 @@
         </is>
       </c>
       <c r="B83" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="C83" t="n">
-        <v>31.3</v>
+        <v>31.8</v>
       </c>
       <c r="D83" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="84">
@@ -1761,13 +1761,13 @@
         </is>
       </c>
       <c r="B84" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="C84" t="n">
-        <v>31.9</v>
+        <v>32.3</v>
       </c>
       <c r="D84" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="85">
@@ -1777,13 +1777,13 @@
         </is>
       </c>
       <c r="B85" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="C85" t="n">
-        <v>32.6</v>
+        <v>28.1</v>
       </c>
       <c r="D85" t="n">
-        <v>0.3</v>
+        <v>9</v>
       </c>
     </row>
     <row r="86">
@@ -1796,7 +1796,7 @@
         <v>46276</v>
       </c>
       <c r="C86" t="n">
-        <v>18.2</v>
+        <v>18.3</v>
       </c>
       <c r="D86" t="n">
         <v>0</v>
@@ -1844,7 +1844,7 @@
         <v>46279</v>
       </c>
       <c r="C89" t="n">
-        <v>26.5</v>
+        <v>26.9</v>
       </c>
       <c r="D89" t="n">
         <v>0</v>
@@ -1860,7 +1860,7 @@
         <v>46280</v>
       </c>
       <c r="C90" t="n">
-        <v>22.3</v>
+        <v>25.4</v>
       </c>
       <c r="D90" t="n">
         <v>0</v>
@@ -1876,7 +1876,7 @@
         <v>46281</v>
       </c>
       <c r="C91" t="n">
-        <v>15.4</v>
+        <v>15.2</v>
       </c>
       <c r="D91" t="n">
         <v>0</v>
@@ -1892,7 +1892,7 @@
         <v>46282</v>
       </c>
       <c r="C92" t="n">
-        <v>17</v>
+        <v>16.2</v>
       </c>
       <c r="D92" t="n">
         <v>0</v>
@@ -1908,10 +1908,10 @@
         <v>46276</v>
       </c>
       <c r="C93" t="n">
-        <v>19.6</v>
+        <v>20.4</v>
       </c>
       <c r="D93" t="n">
-        <v>85.3</v>
+        <v>52.7</v>
       </c>
     </row>
     <row r="94">
@@ -1924,10 +1924,10 @@
         <v>46277</v>
       </c>
       <c r="C94" t="n">
-        <v>25.8</v>
+        <v>25.9</v>
       </c>
       <c r="D94" t="n">
-        <v>0</v>
+        <v>14.3</v>
       </c>
     </row>
     <row r="95">
@@ -1940,10 +1940,10 @@
         <v>46278</v>
       </c>
       <c r="C95" t="n">
-        <v>26.6</v>
+        <v>25.4</v>
       </c>
       <c r="D95" t="n">
-        <v>0.33</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="96">
@@ -1959,7 +1959,7 @@
         <v>30.1</v>
       </c>
       <c r="D96" t="n">
-        <v>0.6000000000000001</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="97">
@@ -1972,10 +1972,10 @@
         <v>46280</v>
       </c>
       <c r="C97" t="n">
-        <v>27.9</v>
+        <v>27.3</v>
       </c>
       <c r="D97" t="n">
-        <v>22.5</v>
+        <v>18.9</v>
       </c>
     </row>
     <row r="98">
@@ -1988,10 +1988,10 @@
         <v>46281</v>
       </c>
       <c r="C98" t="n">
-        <v>25</v>
+        <v>25.8</v>
       </c>
       <c r="D98" t="n">
-        <v>2.5</v>
+        <v>6.699999999999999</v>
       </c>
     </row>
     <row r="99">
@@ -2004,10 +2004,10 @@
         <v>46282</v>
       </c>
       <c r="C99" t="n">
-        <v>25.1</v>
+        <v>24.7</v>
       </c>
       <c r="D99" t="n">
-        <v>2</v>
+        <v>2.6</v>
       </c>
     </row>
     <row r="100">
@@ -2052,10 +2052,10 @@
         <v>46277</v>
       </c>
       <c r="C102" t="n">
-        <v>24.7</v>
+        <v>24.2</v>
       </c>
       <c r="D102" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="103">
@@ -2068,10 +2068,10 @@
         <v>46278</v>
       </c>
       <c r="C103" t="n">
-        <v>28.1</v>
+        <v>27.7</v>
       </c>
       <c r="D103" t="n">
-        <v>0.8</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="104">
@@ -2084,7 +2084,7 @@
         <v>46279</v>
       </c>
       <c r="C104" t="n">
-        <v>19.7</v>
+        <v>19.4</v>
       </c>
       <c r="D104" t="n">
         <v>0</v>
@@ -2100,10 +2100,10 @@
         <v>46280</v>
       </c>
       <c r="C105" t="n">
-        <v>29.9</v>
+        <v>26.6</v>
       </c>
       <c r="D105" t="n">
-        <v>8.5</v>
+        <v>10.8</v>
       </c>
     </row>
     <row r="106">
@@ -2116,7 +2116,7 @@
         <v>46281</v>
       </c>
       <c r="C106" t="n">
-        <v>23</v>
+        <v>23.4</v>
       </c>
       <c r="D106" t="n">
         <v>3.9</v>
